--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42B.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLII/LTAIPT_A63F42B.xlsx
@@ -10,17 +10,19 @@
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
     <sheet name="Hidden_1" sheetId="2" r:id="rId2"/>
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
+    <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_14">Hidden_1!$A$1:$A$4</definedName>
-    <definedName name="Hidden_210">Hidden_2!$A$1:$A$6</definedName>
+    <definedName name="Hidden_29">Hidden_2!$A$1:$A$2</definedName>
+    <definedName name="Hidden_311">Hidden_3!$A$1:$A$6</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
   <si>
     <t>49013</t>
   </si>
@@ -85,6 +87,9 @@
     <t>437020</t>
   </si>
   <si>
+    <t>571945</t>
+  </si>
+  <si>
     <t>437024</t>
   </si>
   <si>
@@ -130,6 +135,9 @@
     <t>Segundo apellido</t>
   </si>
   <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
     <t>Monto de la porción de su pensión que recibe directamente del Estado Mexicano</t>
   </si>
   <si>
@@ -148,7 +156,7 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
@@ -157,19 +165,19 @@
     <t>Departamento de Recursos Humanos</t>
   </si>
   <si>
-    <t>99BF3222FE5D0F472AE80F352AECED53</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>14/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el período del 01 de julio de 2022 al 30 de septuiembere de 2022, el listado de jubilados y pensionados es generado y publicado por el Instituto de Seguridad Social al Servicio de los Trabajadores del Estado como parte de las prestaciones de Ley que derivan del esquema de seguridad social prevista en la Ley del Instituto de Seguridad Social al Servicio de los Trabajadores del Estado, toda vez que el Colegio de Bachilleres del Estado de Tlaxcala no tiene un esquema propio de jubilaciones y pensiones.</t>
+    <t>E4444B84A161EF519F073C783EFC21FB</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>13/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el período del 01 de julio de 2023 al 30 de septiembre de 2023, el listado de jubilados y pensionados es generado y publicado por el Instituto de Seguridad Social al Servicio de los Trabajadores del Estado como parte de las prestaciones de Ley que derivan del esquema de seguridad social prevista en la Ley del Instituto de Seguridad Social al Servicio de los Trabajadores del Estado, toda vez que el Colegio de Bachilleres del Estado de Tlaxcala no tiene un esquema propio de jubilaciones y pensiones.</t>
   </si>
   <si>
     <t>Jubilado(a)</t>
@@ -182,6 +190,12 @@
   </si>
   <si>
     <t>Otro</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujer</t>
   </si>
   <si>
     <t>Quincenal</t>
@@ -592,10 +606,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.85546875" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -604,20 +618,21 @@
     <col min="7" max="7" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="68.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="73.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="255" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="68.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="73.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -634,7 +649,7 @@
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -649,7 +664,7 @@
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -675,25 +690,28 @@
         <v>6</v>
       </c>
       <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
         <v>10</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>8</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>9</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>7</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>11</v>
       </c>
-      <c r="O4" t="s">
+      <c r="P4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -736,10 +754,13 @@
       <c r="O5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -755,101 +776,108 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-    </row>
-    <row r="7" spans="1:15" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="P6" s="4"/>
+    </row>
+    <row r="7" spans="1:16" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>42</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="N8" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:O6"/>
+    <mergeCell ref="A6:P6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -857,12 +885,15 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E198">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E8:E199">
       <formula1>Hidden_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K8:K198">
-      <formula1>Hidden_210</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J8:J199">
+      <formula1>Hidden_29</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L199">
+      <formula1>Hidden_311</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -876,22 +907,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -901,37 +932,57 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
